--- a/出力/パイプライン不足分析_20261006.xlsx
+++ b/出力/パイプライン不足分析_20261006.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.600000000000001" customWidth="1" min="1" max="1"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AC=アカデミア, BT/BTL=企業(バイオ), PHM=企業(製薬)</t>
+          <t>AC=アカデミア, BT=バイオテック企業, PHM=製薬企業</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>仮置き</t>
+          <t>確定(10/6確認)</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>納期確度</t>
+          <t>顧客ジャンル BTL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A/B/C(Aが高い想定)</t>
+          <t>定義外のため BT(バイオテック企業)扱い</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -866,61 +866,61 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>代理店</t>
+          <t>列対応</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>一次店の判定</t>
+          <t>納期確度</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>主要一次店(富士フイルム和光純薬・レスター・池田理化・ナカライテスク・バイオテック・ラボ・カーク・アズバイオ)を含めばそれを一次店、無ければ末尾を一次店</t>
+          <t>A=月決, B=Q決, C=未定</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>仮置き</t>
+          <t>確定(10/6確認)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>代理店</t>
+          <t>挽回シナリオ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BTL</t>
+          <t>率</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>バイオテック・ラボの略と解釈</t>
+          <t>Backup昇格15%・引き戻し10%・リード商談化2%(厳しめ設定)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>仮置き</t>
+          <t>確定(10/6確認)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>上期▲7台</t>
+          <t>代理店</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>扱い</t>
+          <t>一次店の判定</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9F目標60台=1H実績11台+下期49台。9F達成=上期▲7台(7F比)の挽回と同義として扱う</t>
+          <t>主要一次店(富士フイルム和光純薬・レスター・池田理化・ナカライテスク・バイオテック・ラボ・カーク・アズバイオ)を含めばそれを一次店、無ければ末尾を一次店</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -932,42 +932,86 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>商談期限</t>
+          <t>代理店</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>目安</t>
+          <t>BTL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>High(ID/FP): アカデミア11月・企業1月 / Low-Mid(SH/MA/SA): アカデミア12月・企業1月</t>
+          <t>バイオテック・ラボの略と解釈</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>確定(Sep資料 slide3)</t>
+          <t>仮置き</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>上期▲7台</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>9F目標60台に含まれる(1H実績11台+下期49台)。9F達成=上期▲7台の挽回</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>確定(10/6確認)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>商談期限</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>目安</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>High(ID/FP): アカデミア11月・企業1月 / Low-Mid(SH/MA/SA): アカデミア12月・企業1月</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>確定(Sep資料 slide3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>個人情報</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>出力方針</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>施設名・個人名・自由記述原文は出力しない。案件はスナップショットのExcel行番号(案件ID)で参照</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
@@ -1149,7 +1193,7 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12.8" customWidth="1" min="5" max="5"/>
     <col width="28.8" customWidth="1" min="6" max="6"/>
-    <col width="11.2" customWidth="1" min="7" max="7"/>
+    <col width="12.8" customWidth="1" min="7" max="7"/>
     <col width="9.600000000000001" customWidth="1" min="8" max="8"/>
     <col width="9.600000000000001" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
@@ -1304,7 +1348,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1384,7 +1428,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A(月決)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1444,7 +1488,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1460,7 +1504,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1528,7 +1572,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>企業(製薬)</t>
+          <t>製薬企業</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1544,7 +1588,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1604,7 +1648,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1620,7 +1664,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1704,7 +1748,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B(Q決)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1764,7 +1808,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1780,7 +1824,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1860,7 +1904,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1944,7 +1988,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2028,7 +2072,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2096,7 +2140,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2112,7 +2156,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A(月決)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2180,7 +2224,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2196,7 +2240,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2284,7 +2328,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2364,7 +2408,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2440,7 +2484,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2516,7 +2560,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2576,7 +2620,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2592,7 +2636,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2652,7 +2696,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>企業(製薬)</t>
+          <t>製薬企業</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2668,7 +2712,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2748,7 +2792,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2828,7 +2872,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2888,7 +2932,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>企業(製薬)</t>
+          <t>製薬企業</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2904,7 +2948,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2972,7 +3016,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3140,7 +3184,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3200,7 +3244,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>企業(製薬)</t>
+          <t>製薬企業</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3216,7 +3260,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3292,7 +3336,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3372,7 +3416,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3436,7 +3480,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3452,7 +3496,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3608,7 +3652,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3668,7 +3712,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3684,7 +3728,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3772,7 +3816,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3852,7 +3896,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3940,7 +3984,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4024,7 +4068,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4108,7 +4152,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4192,7 +4236,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4272,7 +4316,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4336,7 +4380,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -4428,7 +4472,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4508,7 +4552,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4588,7 +4632,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4668,7 +4712,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4732,7 +4776,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -4748,7 +4792,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4832,7 +4876,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4908,7 +4952,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4992,7 +5036,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5072,7 +5116,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5152,7 +5196,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5216,7 +5260,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -5360,7 +5404,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>企業(製薬)</t>
+          <t>製薬企業</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -5376,7 +5420,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5460,7 +5504,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5548,7 +5592,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5628,7 +5672,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5716,7 +5760,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5800,7 +5844,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5884,7 +5928,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A(月決)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5968,7 +6012,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6036,7 +6080,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -6052,7 +6096,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6136,7 +6180,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6196,7 +6240,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -6212,7 +6256,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6352,7 +6396,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -6368,7 +6412,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6528,7 +6572,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6592,7 +6636,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -6608,7 +6652,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6692,7 +6736,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6756,7 +6800,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -6844,7 +6888,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6912,7 +6956,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>企業(製薬)</t>
+          <t>製薬企業</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -7004,7 +7048,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7064,7 +7108,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -7080,7 +7124,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7212,7 +7256,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -7228,7 +7272,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7308,7 +7352,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7464,7 +7508,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7544,7 +7588,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7620,7 +7664,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7696,7 +7740,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7772,7 +7816,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7848,7 +7892,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7988,7 +8032,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -8004,7 +8048,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8088,7 +8132,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8160,7 +8204,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -8176,7 +8220,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8256,7 +8300,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8336,7 +8380,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8416,7 +8460,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8500,7 +8544,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8580,7 +8624,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8660,7 +8704,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8740,7 +8784,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8804,7 +8848,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -9052,7 +9096,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9120,7 +9164,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>企業(製薬)</t>
+          <t>製薬企業</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -9136,7 +9180,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9220,7 +9264,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9300,7 +9344,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9432,7 +9476,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -9508,7 +9552,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -9524,7 +9568,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -9600,7 +9644,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -9680,7 +9724,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9744,7 +9788,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -9760,7 +9804,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9840,7 +9884,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9908,7 +9952,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -9924,7 +9968,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9992,7 +10036,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -10008,7 +10052,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -10088,7 +10132,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -10152,7 +10196,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>企業(バイオ)</t>
+          <t>バイオテック企業</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -10168,7 +10212,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10248,7 +10292,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -10328,7 +10372,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C(未定)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -10595,7 +10639,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>昇格判定完了、昇格30%(仮置き)</t>
+          <t>昇格判定完了、昇格15%以上</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -13882,12 +13926,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41.6" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12.8" customWidth="1" min="3" max="3"/>
+    <col width="20.8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
@@ -13947,15 +13991,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30%(仮置き)</t>
+          <t>昇格15%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>対象40件 × 昇格率30% × (モデル勝率−10%)</t>
+          <t>対象40件 × 昇格率15% × (モデル勝率−10%)</t>
         </is>
       </c>
     </row>
@@ -13970,15 +14014,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20%(仮置き)</t>
+          <t>引き戻し10%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.99</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9F以降に来期へ移った54件 × 引き戻し率20% × モデル勝率</t>
+          <t>9F以降に来期へ移った54件 × 引き戻し率10% × モデル勝率</t>
         </is>
       </c>
     </row>
@@ -13989,19 +14033,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FCT化32%</t>
+          <t>商談化2%・FCT化32%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.24</v>
+        <v>1.45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>標準ケース13商談(slide7) × FCT化率32%(slide4: 30/94) × 平均勝率0.54</t>
+          <t>422名 × 商談化2%≒8.4商談(slide7保守ケース相当) × FCT化32%(slide4: 30/94) × 平均勝率0.54</t>
         </is>
       </c>
     </row>
@@ -14012,19 +14056,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FCT化32%</t>
+          <t>商談化2%・FCT化32%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>148件 × 商談化3%(仮置き)≒4商談 × 32% × 0.54</t>
+          <t>148件 × 2%≒3.0商談 × 32% × 0.54</t>
         </is>
       </c>
     </row>
@@ -14035,19 +14079,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FCT化32%</t>
+          <t>商談化2%・FCT化32%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.52</v>
+        <v>0.76</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FY25-Q2展示会110リード(slide3)×商談化3%(仮置き)≒3商談 × 32% × 0.54</t>
+          <t>110リード(FY25-Q2展示会実績)×2回 × 2%≒4.4商談 × 32% × 0.54</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14104,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>15.32</v>
+        <v>8.66</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -14077,11 +14121,30 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>-0.37</v>
+        <v>6.29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>不足 − 合計(正なら未充足)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>参考: 不足を埋める昇格率・引き戻し率</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>昇格31%・引き戻し21%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>インハウス施策は据え置き、①②の率を同じ倍率(2.1倍)で引き上げた場合</t>
         </is>
       </c>
     </row>
